--- a/現場確認日_安全対策一覧_7-9月分.xlsx
+++ b/現場確認日_安全対策一覧_7-9月分.xlsx
@@ -11,7 +11,7 @@
     <sheet name="現場確認日一覧" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="安全対策（類型別）" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="月別集計" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="参考（現地か不明）" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="参考（現場確認から除外）" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">現場確認日一覧!$4:$4</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="165">
   <si>
     <r>
       <rPr>
@@ -1961,7 +1961,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">参考：現地で実施した可能性があるが、日報からは判断できない業務（一覧・集計には含めていない）</t>
+    <t xml:space="preserve">参考：現地での実施か日報から判断できなかった業務 → 実施場所を確認のうえ現場確認から除外（一覧・集計には含めていない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実施場所</t>
   </si>
   <si>
     <t xml:space="preserve">除外理由</t>
@@ -1973,15 +1976,15 @@
     <t xml:space="preserve">浅茂川海岸なぎさ緊急保全工事</t>
   </si>
   <si>
-    <t xml:space="preserve">工事完成下検査は書面中心と考えられるが、現地確認を含む可能性がある</t>
+    <t xml:space="preserve">河川砂防課</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実施場所が河川砂防課（事務所内）のため、現場確認に該当しない</t>
   </si>
   <si>
     <t xml:space="preserve">工事着手前打合せ</t>
   </si>
   <si>
-    <t xml:space="preserve">打合せ場所の記載がない</t>
-  </si>
-  <si>
     <t xml:space="preserve">竹野川他府民協働インフラ工事</t>
   </si>
   <si>
@@ -1995,6 +1998,9 @@
   </si>
   <si>
     <t xml:space="preserve">㈱丸正組</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 実施場所は確認結果により記入（日報本文には記載なし）。</t>
   </si>
 </sst>
 </file>
@@ -5395,7 +5401,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5404,7 +5410,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5437,6 +5444,9 @@
       <c r="H3" s="4" t="s">
         <v>152</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -5449,10 +5459,10 @@
         <v>45</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>24</v>
@@ -5461,7 +5471,10 @@
         <v>25</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5478,7 +5491,7 @@
         <v>92</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>24</v>
@@ -5487,6 +5500,9 @@
         <v>34</v>
       </c>
       <c r="H5" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>157</v>
       </c>
     </row>
@@ -5501,10 +5517,10 @@
         <v>45</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>24</v>
@@ -5513,7 +5529,10 @@
         <v>25</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5524,22 +5543,30 @@
         <v>121</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>57</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H7" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
